--- a/data/samples/student_progress.xlsx
+++ b/data/samples/student_progress.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,16 @@
           <t>updated_at</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>carryover_type_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>carryover_question_ids</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -524,8 +534,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -539,6 +547,12 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -583,8 +597,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -598,6 +610,12 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -642,8 +660,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -657,6 +673,12 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -701,8 +723,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -716,6 +736,12 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -760,8 +786,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -775,6 +799,12 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -819,8 +849,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -834,6 +862,12 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -878,8 +912,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -893,6 +925,12 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -937,8 +975,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -952,6 +988,12 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -996,8 +1038,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1011,6 +1051,12 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1055,8 +1101,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1070,6 +1114,12 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1114,8 +1164,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1129,6 +1177,12 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1173,8 +1227,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1188,6 +1240,12 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1232,8 +1290,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1247,6 +1303,12 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1291,8 +1353,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1306,6 +1366,12 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1350,8 +1416,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1365,6 +1429,12 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1409,8 +1479,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1424,6 +1492,12 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1468,8 +1542,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1483,6 +1555,12 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1527,8 +1605,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1542,6 +1618,12 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1586,8 +1668,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1601,6 +1681,12 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1645,8 +1731,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1660,6 +1744,12 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1704,8 +1794,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1719,6 +1807,12 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1763,8 +1857,6 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1778,6 +1870,12 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>2026-06-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
